--- a/ET/Unity/Assets/Config/Excel/TargetFinderConfig.xlsx
+++ b/ET/Unity/Assets/Config/Excel/TargetFinderConfig.xlsx
@@ -26,8 +26,35 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>ShapeType 2=圆形，3=矩形，4=扇形
+AnchorType 1=施法者，2=当前目标
+Param1 半径/矩形长度/扇形半径，int/100
+Param2 矩形宽度/扇形角度，int/100
+OffsetX中心点偏移X，int/100
+OffsetY中心点偏移Y，int/100</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
   <si>
     <t>ID</t>
   </si>
@@ -38,6 +65,21 @@
     <t>搜索范围</t>
   </si>
   <si>
+    <t>锚点类型</t>
+  </si>
+  <si>
+    <t>参数1</t>
+  </si>
+  <si>
+    <t>参数2</t>
+  </si>
+  <si>
+    <t>偏移X</t>
+  </si>
+  <si>
+    <t>偏移Y</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -45,6 +87,21 @@
   </si>
   <si>
     <t>Range</t>
+  </si>
+  <si>
+    <t>AnchorType</t>
+  </si>
+  <si>
+    <t>Param1</t>
+  </si>
+  <si>
+    <t>Param2</t>
+  </si>
+  <si>
+    <t>OffsetX</t>
+  </si>
+  <si>
+    <t>OffsetY</t>
   </si>
   <si>
     <t>int</t>
@@ -60,7 +117,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -69,11 +126,27 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF5C4A32"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF6B5B44"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF6B5B44"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -219,8 +292,13 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -229,6 +307,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC9B896"/>
+        <bgColor rgb="FFC9B896"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6DCC4"/>
+        <bgColor rgb="FFE6DCC4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0E8D8"/>
+        <bgColor rgb="FFF0E8D8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -414,12 +510,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD5CBB5"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD5CBB5"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD5CBB5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD5CBB5"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -523,28 +634,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -553,123 +655,141 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1016,59 +1136,146 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="C3:J7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="11.5" customWidth="1"/>
+    <col min="4" max="10" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:5">
-      <c r="C3" t="s">
+    <row r="3" spans="3:10">
+      <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="F3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="3:5">
-      <c r="C4" t="s">
+    <row r="4" spans="3:10">
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="3:10">
+      <c r="C5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="3:10">
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>300</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:10">
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
         <v>3</v>
       </c>
-      <c r="D4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="3:5">
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="3:5">
-      <c r="C6">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>1</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>300</v>
+      <c r="G7">
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <v>80</v>
+      </c>
+      <c r="I7">
+        <v>62</v>
+      </c>
+      <c r="J7">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>